--- a/Loan_Info.xlsx
+++ b/Loan_Info.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="Loan_Info"/>
   </sheets>
   <definedNames>
-    <definedName name="Loan_Info">'Loan_Info'!$A$1:$W$1404</definedName>
+    <definedName name="Loan_Info">'Loan_Info'!$A$1:$W$1406</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -347,7 +347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W1404"/>
+  <dimension ref="A1:W1406"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -79535,11 +79535,11 @@
         <v>1487</v>
       </c>
       <c r="B1404" s="0">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C1404" s="0" t="inlineStr">
         <is>
-          <t>asim</t>
+          <t>Daniel Weyant</t>
         </is>
       </c>
       <c r="D1404" s="0" t="inlineStr">
@@ -79549,22 +79549,22 @@
       </c>
       <c r="E1404" s="0" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Refinance</t>
         </is>
       </c>
       <c r="F1404" s="0" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Brokered</t>
         </is>
       </c>
       <c r="G1404" s="0">
-        <v>2500</v>
+        <v>281000</v>
       </c>
       <c r="H1404" s="0">
         <v>0</v>
       </c>
       <c r="K1404" s="1">
-        <v>46192</v>
+        <v>46062</v>
       </c>
       <c r="L1404" s="0">
         <v>2</v>
@@ -79586,7 +79586,7 @@
       </c>
       <c r="S1404" s="0" t="inlineStr">
         <is>
-          <t>Brian Thomas</t>
+          <t>Griffin Dutson</t>
         </is>
       </c>
       <c r="V1404" s="0">
@@ -79594,7 +79594,143 @@
       </c>
       <c r="W1404" s="0" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>Sam Larson</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1405">
+      <c r="A1405" s="0">
+        <v>1488</v>
+      </c>
+      <c r="B1405" s="0">
+        <v>19</v>
+      </c>
+      <c r="C1405" s="0" t="inlineStr">
+        <is>
+          <t>Earl Davis</t>
+        </is>
+      </c>
+      <c r="D1405" s="0" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
+      <c r="E1405" s="0" t="inlineStr">
+        <is>
+          <t>Refinance</t>
+        </is>
+      </c>
+      <c r="F1405" s="0" t="inlineStr">
+        <is>
+          <t>Brokered</t>
+        </is>
+      </c>
+      <c r="G1405" s="0">
+        <v>480500</v>
+      </c>
+      <c r="H1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="K1405" s="1">
+        <v>46080</v>
+      </c>
+      <c r="L1405" s="0">
+        <v>2</v>
+      </c>
+      <c r="M1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="N1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="O1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="P1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="S1405" s="0" t="inlineStr">
+        <is>
+          <t>Griffin Dutson</t>
+        </is>
+      </c>
+      <c r="V1405" s="0">
+        <v>0</v>
+      </c>
+      <c r="W1405" s="0" t="inlineStr">
+        <is>
+          <t>Sam Larson</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1406">
+      <c r="A1406" s="0">
+        <v>1489</v>
+      </c>
+      <c r="B1406" s="0">
+        <v>19</v>
+      </c>
+      <c r="C1406" s="0" t="inlineStr">
+        <is>
+          <t>Brett Bunderson</t>
+        </is>
+      </c>
+      <c r="D1406" s="0" t="inlineStr">
+        <is>
+          <t>Conventional</t>
+        </is>
+      </c>
+      <c r="E1406" s="0" t="inlineStr">
+        <is>
+          <t>Refinance</t>
+        </is>
+      </c>
+      <c r="F1406" s="0" t="inlineStr">
+        <is>
+          <t>Brokered</t>
+        </is>
+      </c>
+      <c r="G1406" s="0">
+        <v>455500</v>
+      </c>
+      <c r="H1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="K1406" s="1">
+        <v>46092</v>
+      </c>
+      <c r="L1406" s="0">
+        <v>2</v>
+      </c>
+      <c r="M1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="N1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="O1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="P1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="S1406" s="0" t="inlineStr">
+        <is>
+          <t>Griffin Dutson</t>
+        </is>
+      </c>
+      <c r="V1406" s="0">
+        <v>0</v>
+      </c>
+      <c r="W1406" s="0" t="inlineStr">
+        <is>
+          <t>Adam Larson</t>
         </is>
       </c>
     </row>
